--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104735_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104735_W31.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7984</v>
+        <v>8.303900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3451</v>
+        <v>7.0465</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4533</v>
+        <v>1.2574</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9638</v>
+        <v>5.9587</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4155</v>
+        <v>1.4158</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5483</v>
+        <v>4.5429</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9489</v>
+        <v>6.9316</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9033</v>
+        <v>2.8958</v>
       </c>
       <c r="L2" t="n">
-        <v>4.0457</v>
+        <v>4.0358</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9851</v>
+        <v>-0.9729</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4877</v>
+        <v>-1.48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5026</v>
+        <v>0.5071</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3336</v>
+        <v>0.8492</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8329</v>
+        <v>-0.1048</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1665</v>
+        <v>0.954</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4744</v>
+        <v>3.9339</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2338</v>
+        <v>2.8975</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2406</v>
+        <v>1.0363</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7973</v>
+        <v>-0.2208</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9484</v>
+        <v>0.4598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1511</v>
+        <v>-0.6806</v>
       </c>
       <c r="J3" t="n">
-        <v>4.879</v>
+        <v>0.993</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7299</v>
+        <v>0.7477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1491</v>
+        <v>0.2453</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0817</v>
+        <v>-1.2138</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7814</v>
+        <v>-0.2879</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3002</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7262</v>
+        <v>-0.4553</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8175</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.972</v>
+        <v>1.0652</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4673</v>
+        <v>0.1808</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5048</v>
+        <v>0.8843</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3862</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3862</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9409</v>
+        <v>3.9302</v>
       </c>
       <c r="E4" t="n">
-        <v>1.83</v>
+        <v>1.8235</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1109</v>
+        <v>2.1067</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2203</v>
+        <v>3.7908</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4621</v>
+        <v>3.9361</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6824</v>
+        <v>-0.1452</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0041</v>
+        <v>4.8611</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7552</v>
+        <v>4.7122</v>
       </c>
       <c r="L4" t="n">
-        <v>0.249</v>
+        <v>0.1489</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2244</v>
+        <v>-1.0703</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2931</v>
+        <v>-0.7761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9314</v>
+        <v>-0.2942</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4544</v>
+        <v>-2.7316</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0699</v>
+        <v>1.4368</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9023</v>
+        <v>0.0809</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9722</v>
+        <v>1.3559</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1825</v>
+        <v>-0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1825</v>
+        <v>-0.387</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6214</v>
+        <v>1.3355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3442</v>
+        <v>0.0514</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2772</v>
+        <v>1.2842</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9003</v>
+        <v>0.9014</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5102</v>
+        <v>0.5111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3901</v>
+        <v>0.3903</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2448</v>
+        <v>1.2433</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L5" t="n">
-        <v>1.193</v>
+        <v>1.1916</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3446</v>
+        <v>-0.3419</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4583</v>
+        <v>0.4593</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.8012</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5617</v>
+        <v>0.2764</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3031</v>
+        <v>0.0161</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2587</v>
+        <v>0.2603</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5613</v>
+        <v>0.0463</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3614</v>
+        <v>-1.3347</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8</v>
+        <v>1.3811</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8451</v>
+        <v>-0.9596</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0436</v>
+        <v>-1.5541</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8015</v>
+        <v>0.5945</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9774</v>
+        <v>-0.7167</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9107</v>
+        <v>-0.6345</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.888</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8677</v>
+        <v>-0.243</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9543</v>
+        <v>-0.9196</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0866</v>
+        <v>0.6766</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3631</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5903</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4742</v>
+        <v>0.0256</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8143</v>
+        <v>-0.3904</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.416</v>
       </c>
       <c r="V6" t="n">
-        <v>0.705</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8875</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1825</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3964</v>
+        <v>0.0225</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9053</v>
+        <v>1.0529</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5089</v>
+        <v>-1.0304</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7693</v>
+        <v>-1.8484</v>
       </c>
       <c r="H7" t="n">
-        <v>0.16</v>
+        <v>-0.0457</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9294</v>
+        <v>-1.8027</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.9897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0.9028</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7143</v>
+        <v>-1.8925</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0723</v>
+        <v>-0.8587</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1427</v>
+        <v>-0.9485</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.215</v>
+        <v>0.0898</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4544</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4544</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0814</v>
+        <v>0.9407</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2082</v>
+        <v>0.5269</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1268</v>
+        <v>0.4138</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.8814</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4554</v>
+        <v>-0.489</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6352</v>
+        <v>-0.907</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1797</v>
+        <v>0.4181</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9637</v>
+        <v>-0.7689</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5576</v>
+        <v>0.1607</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5938</v>
+        <v>-0.9296</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7139</v>
+        <v>-0.6979</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6334</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0806</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2498</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9242</v>
+        <v>0.1435</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6744</v>
+        <v>-0.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1359</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4683</v>
+        <v>-0.1754</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2258</v>
+        <v>0.0338</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5807</v>
+        <v>-0.6912</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5794</v>
+        <v>-0.8037</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0013</v>
+        <v>0.1125</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5188</v>
+        <v>-2.0906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6868</v>
+        <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2056</v>
+        <v>-2.2033</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0419</v>
+        <v>-0.6175</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2503</v>
+        <v>0.7165</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2921</v>
+        <v>-1.334</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.477</v>
+        <v>-1.4731</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5635</v>
+        <v>-0.6037</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0866</v>
+        <v>-0.8694</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4544</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5934</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.5369</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.5447</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.4544</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.5751</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.3031</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.272</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.0913</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1594</v>
-      </c>
       <c r="X9" t="n">
-        <v>-1.2507</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2821</v>
+        <v>-1.2303</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9399</v>
+        <v>-0.9947</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3423</v>
+        <v>-0.2356</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0849</v>
+        <v>-1.5208</v>
       </c>
       <c r="H10" t="n">
-        <v>0.118</v>
+        <v>0.6839</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2029</v>
+        <v>-2.2046</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6022</v>
+        <v>-1.0501</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7266</v>
+        <v>1.2443</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3288</v>
+        <v>-2.2945</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4827</v>
+        <v>-0.4706</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6086</v>
+        <v>-0.5604</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8741</v>
+        <v>0.0898</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5903</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0147</v>
+        <v>0.9247</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1105</v>
+        <v>-0.1024</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0958</v>
+        <v>1.027</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5456</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5456</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7391</v>
+        <v>-2.6833</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3222</v>
+        <v>-1.4956</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4169</v>
+        <v>-1.1877</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7129</v>
+        <v>-0.7101</v>
       </c>
       <c r="H11" t="n">
-        <v>0.024</v>
+        <v>0.0256</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.737</v>
+        <v>-0.7358</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1233</v>
+        <v>-0.1249</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0689</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1924</v>
+        <v>-0.1939</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5897</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0451</v>
+        <v>-0.0433</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5446</v>
+        <v>-0.5419</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1332</v>
+        <v>0.1846</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1642</v>
+        <v>-0.0049</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.031</v>
+        <v>0.1895</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8568</v>
+        <v>-2.7017</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4173</v>
+        <v>-3.4303</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5605</v>
+        <v>0.7286</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3057</v>
+        <v>-0.301</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5232</v>
       </c>
       <c r="I12" t="n">
-        <v>0.221</v>
+        <v>0.2221</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3169</v>
+        <v>0.3143</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3975</v>
+        <v>0.3964</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0806</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6226</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9242</v>
+        <v>-0.9196</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3016</v>
+        <v>0.3043</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4386</v>
+        <v>-0.2821</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4858</v>
+        <v>-0.4879</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0472</v>
+        <v>0.2058</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1678</v>
+        <v>-3.8114</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-1.2463</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.635</v>
+        <v>-2.5651</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6484</v>
+        <v>-1.6452</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6657</v>
+        <v>-1.6631</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0173</v>
+        <v>0.018</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.6979</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7716</v>
+        <v>-0.7724</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9514</v>
+        <v>-0.9472</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8941</v>
+        <v>-0.8907</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0573</v>
+        <v>-0.0565</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0263</v>
+        <v>0.3785</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3002</v>
+        <v>0.5898</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2739</v>
+        <v>-0.2113</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.918100000000001</v>
+        <v>5.9654</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7824</v>
+        <v>2.6595</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1356</v>
+        <v>3.306100000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5922999999999989</v>
+        <v>0.5854999999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5314</v>
+        <v>3.519600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.939400000000001</v>
+        <v>-2.934</v>
       </c>
       <c r="J14" t="n">
-        <v>9.540799999999999</v>
+        <v>9.448599999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>10.4067</v>
+        <v>10.3466</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8653999999999996</v>
+        <v>-0.898199999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.949</v>
+        <v>-8.863100000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.8752</v>
+        <v>-6.827</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0737</v>
+        <v>-2.0359</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1359</v>
+        <v>-1.138</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.7671</v>
+        <v>-14.7961</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6312</v>
+        <v>13.6581</v>
       </c>
       <c r="S14" t="n">
-        <v>5.143000000000001</v>
+        <v>6.2025</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8815999999999999</v>
+        <v>0.1364</v>
       </c>
       <c r="U14" t="n">
-        <v>6.0247</v>
+        <v>6.066000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3186999999999995</v>
+        <v>0.3155000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.890099999999999</v>
+        <v>7.8704</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.571400000000001</v>
+        <v>-7.5547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2006</v>
+        <v>3.4249</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1325</v>
+        <v>4.7913</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0681</v>
+        <v>-1.3663</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0251</v>
+        <v>3.6282</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1533</v>
+        <v>0.5222</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1784</v>
+        <v>3.106</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0959</v>
+        <v>4.6882</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4614</v>
+        <v>1.672</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3655</v>
+        <v>3.0162</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.121</v>
+        <v>-1.0599</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3081</v>
+        <v>-1.1497</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1871</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4991</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2719</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7427</v>
+        <v>-0.7967</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2837</v>
+        <v>-0.4416</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0263</v>
+        <v>-0.3551</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7103</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8194</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1091</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8716</v>
+        <v>3.06</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5666</v>
+        <v>0.6281</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6949</v>
+        <v>2.432</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6255</v>
+        <v>-0.0299</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5191</v>
+        <v>0.1523</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1063</v>
+        <v>-0.1822</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6961</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6763</v>
+        <v>0.4547</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0198</v>
+        <v>-0.3735</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0706</v>
+        <v>-0.1111</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1571</v>
+        <v>-0.3023</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0866</v>
+        <v>0.1912</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1359</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3442</v>
+        <v>-0.3867</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6751</v>
+        <v>-0.7623</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6691</v>
+        <v>0.3757</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5456</v>
+        <v>3.7042</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5456</v>
+        <v>3.8132</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0913</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4837</v>
+        <v>0.9392</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9298</v>
+        <v>1.0227</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4461</v>
+        <v>-0.0834</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2265</v>
+        <v>1.2239</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7912</v>
+        <v>0.7924</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4354</v>
+        <v>0.4315</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0942</v>
+        <v>2.0826</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7454</v>
+        <v>1.7409</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3488</v>
+        <v>0.3417</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8677</v>
+        <v>-0.8587</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9543</v>
+        <v>-0.9485</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4747</v>
+        <v>-1.0164</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2114</v>
+        <v>-1.0992</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2633</v>
+        <v>0.0827</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0503</v>
+        <v>0.0488</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4101</v>
+        <v>1.405</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3598</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2022</v>
+        <v>0.7155</v>
       </c>
       <c r="E18" t="n">
-        <v>2.503</v>
+        <v>2.7197</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3007</v>
+        <v>-2.0042</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4962</v>
+        <v>3.4949</v>
       </c>
       <c r="H18" t="n">
-        <v>0.29</v>
+        <v>0.2926</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2062</v>
+        <v>3.2024</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5367</v>
+        <v>4.526</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4171</v>
+        <v>1.4134</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1196</v>
+        <v>3.1126</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0405</v>
+        <v>-1.031</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1271</v>
+        <v>-1.1209</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.999</v>
+        <v>-0.4819</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4669</v>
+        <v>-0.2325</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5321</v>
+        <v>-0.2494</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.768</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7042</v>
+        <v>-0.0078</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0638</v>
+        <v>-0.9382</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0313</v>
+        <v>-1.7106</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7408</v>
+        <v>-1.9301</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7722</v>
+        <v>0.2195</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1004</v>
+        <v>0.5547</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5291</v>
+        <v>0.3685</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4287</v>
+        <v>0.1862</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1318</v>
+        <v>-2.2653</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7883</v>
+        <v>-2.2986</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3435</v>
+        <v>0.0333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8175</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0819</v>
+        <v>-0.3752</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4415</v>
+        <v>-0.5625</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3595</v>
+        <v>0.1873</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1091</v>
+        <v>0.2292</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1091</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2222</v>
+        <v>-1.1239</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2336</v>
+        <v>-1.0781</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9887</v>
+        <v>-0.0458</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.716</v>
+        <v>-1.031</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9317</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2157</v>
+        <v>-1.7694</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5614</v>
+        <v>1.0895</v>
       </c>
       <c r="K20" t="n">
-        <v>0.375</v>
+        <v>2.5198</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1864</v>
+        <v>-1.4303</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2774</v>
+        <v>-2.1205</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.3067</v>
+        <v>-1.7814</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0293</v>
+        <v>-0.3391</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9087</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6418</v>
+        <v>-0.4392</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.8018</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1532</v>
+        <v>0.3627</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2268</v>
+        <v>-0.1089</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2268</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6164</v>
+        <v>-1.3926</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6606</v>
+        <v>-2.5113</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0441</v>
+        <v>1.1187</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0853</v>
+        <v>-2.122</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3982</v>
+        <v>-0.7007</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3129</v>
+        <v>-1.4214</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5501</v>
+        <v>-1.3936</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6619</v>
+        <v>-0.0969</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1118</v>
+        <v>-1.2967</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5353</v>
+        <v>-0.7284</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7363</v>
+        <v>-0.6037</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2011</v>
+        <v>-0.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3631</v>
+        <v>1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5903</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5344</v>
+        <v>-0.9827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8833</v>
+        <v>-0.8901</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3489</v>
+        <v>-0.0926</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3598</v>
+        <v>-0.1089</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3598</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8847</v>
+        <v>-1.4613</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6135</v>
+        <v>-1.5508</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7288</v>
+        <v>0.0895</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1203</v>
+        <v>-1.084</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7002</v>
+        <v>-1.3985</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.42</v>
+        <v>0.3145</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3832</v>
+        <v>-0.554</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0916</v>
+        <v>-0.6657</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2915</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7371</v>
+        <v>-0.53</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6086</v>
+        <v>-0.7328</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1285</v>
+        <v>0.2028</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8175</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0447</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4728</v>
+        <v>-0.3869</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0032</v>
+        <v>-0.7692</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4696</v>
+        <v>0.3823</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1091</v>
+        <v>-1.3562</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1091</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0742</v>
+        <v>-3.0075</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8646</v>
+        <v>-2.348</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2097</v>
+        <v>-0.6596</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6407</v>
+        <v>-1.6361</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0143</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6264</v>
+        <v>-1.6268</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0221</v>
+        <v>-2.0248</v>
       </c>
       <c r="K23" t="n">
-        <v>0.121</v>
+        <v>0.1207</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.143</v>
+        <v>-2.1455</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3813</v>
+        <v>0.3887</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1353</v>
+        <v>-0.13</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8171</v>
+        <v>-0.1242</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2022</v>
+        <v>-0.2744</v>
       </c>
       <c r="U23" t="n">
-        <v>0.615</v>
+        <v>0.1503</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3419</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1106</v>
+        <v>-5.1283</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1911</v>
+        <v>-4.9717</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0805</v>
+        <v>-0.1566</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3216</v>
+        <v>-1.319</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9813</v>
+        <v>-1.979</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6597</v>
+        <v>0.66</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1805</v>
+        <v>-0.1866</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6965</v>
+        <v>-0.7002</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5159</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.141</v>
+        <v>-1.1325</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2848</v>
+        <v>-1.2788</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1438</v>
+        <v>0.1463</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1541</v>
+        <v>-0.1672</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4669</v>
+        <v>-0.2325</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3128</v>
+        <v>0.0653</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.917999999999999</v>
+        <v>-4.9201</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.135699999999999</v>
+        <v>-3.3059</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7824</v>
+        <v>-1.6139</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5920999999999996</v>
+        <v>-0.5855999999999997</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.5313</v>
+        <v>-3.5197</v>
       </c>
       <c r="I25" t="n">
-        <v>2.9392</v>
+        <v>2.9341</v>
       </c>
       <c r="J25" t="n">
-        <v>8.9488</v>
+        <v>8.863200000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>6.875299999999999</v>
+        <v>6.827200000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>2.0736</v>
+        <v>2.035999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.541100000000002</v>
+        <v>-9.448699999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.4066</v>
+        <v>-10.3467</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8656999999999999</v>
+        <v>0.898</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1359</v>
+        <v>1.1383</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6312</v>
+        <v>-13.6578</v>
       </c>
       <c r="R25" t="n">
-        <v>14.767</v>
+        <v>14.7961</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.1431</v>
+        <v>-5.157100000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.0247</v>
+        <v>-6.0661</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8815999999999999</v>
+        <v>0.9092</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3186999999999995</v>
+        <v>-0.3153999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>7.571400000000001</v>
+        <v>7.5549</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.890199999999999</v>
+        <v>-7.8703</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104735_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104735_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.5547</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104735_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.8703</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
